--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/07,26/27,07,26 Останкино КИ и ЗПФ/дв 27,07,26 днрсч ост ки.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/07,26/27,07,26 Останкино КИ и ЗПФ/дв 27,07,26 днрсч ост ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\07,26\27,07,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B4DD3A85-8DE0-4B38-A6E4-A66630B4ECC1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E150393C-49B1-49D0-BFA3-C1F64F484A04}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="463" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="464" uniqueCount="194">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -797,7 +797,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -830,6 +830,10 @@
     <xf numFmtId="164" fontId="1" fillId="9" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="9" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="1" fillId="5" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -1542,7 +1546,7 @@
       </c>
       <c r="U5" s="3">
         <f t="shared" si="0"/>
-        <v>12287</v>
+        <v>12207</v>
       </c>
       <c r="V5" s="3">
         <f t="shared" ref="V5" si="1">SUM(V6:V499)</f>
@@ -1593,7 +1597,7 @@
       <c r="AI5" s="6"/>
       <c r="AJ5" s="3">
         <f>SUM(AJ6:AJ499)</f>
-        <v>6194.5400000000009</v>
+        <v>6172.1400000000012</v>
       </c>
       <c r="AK5" s="3">
         <f>SUM(AK6:AK499)</f>
@@ -11725,110 +11729,111 @@
       <c r="AZ86" s="6"/>
     </row>
     <row r="87" spans="1:52" x14ac:dyDescent="0.25">
-      <c r="A87" s="6" t="s">
+      <c r="A87" s="32" t="s">
         <v>137</v>
       </c>
-      <c r="B87" s="6" t="s">
+      <c r="B87" s="32" t="s">
         <v>35</v>
       </c>
-      <c r="C87" s="6">
+      <c r="C87" s="32">
         <v>118</v>
       </c>
-      <c r="D87" s="6">
+      <c r="D87" s="32">
         <v>34</v>
       </c>
-      <c r="E87" s="6">
+      <c r="E87" s="32">
         <v>60</v>
       </c>
-      <c r="F87" s="6">
+      <c r="F87" s="32">
         <v>88</v>
       </c>
-      <c r="G87" s="7">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="H87" s="6">
+      <c r="G87" s="33">
+        <v>0</v>
+      </c>
+      <c r="H87" s="32">
         <v>45</v>
       </c>
-      <c r="I87" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="J87" s="6"/>
-      <c r="K87" s="6">
+      <c r="I87" s="32" t="s">
+        <v>59</v>
+      </c>
+      <c r="J87" s="32"/>
+      <c r="K87" s="32">
         <v>66</v>
       </c>
-      <c r="L87" s="6">
+      <c r="L87" s="32">
         <f t="shared" si="29"/>
         <v>-6</v>
       </c>
-      <c r="M87" s="6">
+      <c r="M87" s="32">
         <f t="shared" si="30"/>
         <v>60</v>
       </c>
-      <c r="N87" s="6"/>
-      <c r="O87" s="6">
-        <v>0</v>
-      </c>
-      <c r="P87" s="6"/>
-      <c r="Q87" s="6"/>
-      <c r="R87" s="6">
+      <c r="N87" s="32"/>
+      <c r="O87" s="32">
+        <v>0</v>
+      </c>
+      <c r="P87" s="32"/>
+      <c r="Q87" s="32"/>
+      <c r="R87" s="32">
         <f t="shared" si="31"/>
         <v>12</v>
       </c>
-      <c r="S87" s="8">
+      <c r="S87" s="34">
         <f t="shared" si="41"/>
         <v>80</v>
       </c>
-      <c r="T87" s="8">
+      <c r="T87" s="34">
         <f t="shared" si="33"/>
         <v>80</v>
       </c>
-      <c r="U87" s="8">
-        <f t="shared" si="34"/>
-        <v>80</v>
-      </c>
-      <c r="V87" s="8"/>
-      <c r="W87" s="19"/>
-      <c r="X87" s="6">
+      <c r="U87" s="34">
+        <v>0</v>
+      </c>
+      <c r="V87" s="34"/>
+      <c r="W87" s="35"/>
+      <c r="X87" s="32">
         <f t="shared" si="35"/>
         <v>14</v>
       </c>
-      <c r="Y87" s="6">
+      <c r="Y87" s="32">
         <f t="shared" si="32"/>
         <v>7.333333333333333</v>
       </c>
-      <c r="Z87" s="6">
+      <c r="Z87" s="32">
         <v>6.8</v>
       </c>
-      <c r="AA87" s="6">
+      <c r="AA87" s="32">
         <v>12.6</v>
       </c>
-      <c r="AB87" s="6">
+      <c r="AB87" s="32">
         <v>14.6</v>
       </c>
-      <c r="AC87" s="6">
+      <c r="AC87" s="32">
         <v>9.1999999999999993</v>
       </c>
-      <c r="AD87" s="6">
+      <c r="AD87" s="32">
         <v>10.8</v>
       </c>
-      <c r="AE87" s="6">
+      <c r="AE87" s="32">
         <v>17.600000000000001</v>
       </c>
-      <c r="AF87" s="6">
+      <c r="AF87" s="32">
         <v>12</v>
       </c>
-      <c r="AG87" s="6">
+      <c r="AG87" s="32">
         <v>16.399999999999999</v>
       </c>
-      <c r="AH87" s="6">
+      <c r="AH87" s="32">
         <v>18.600000000000001</v>
       </c>
-      <c r="AI87" s="6"/>
-      <c r="AJ87" s="6">
+      <c r="AI87" s="32" t="s">
+        <v>189</v>
+      </c>
+      <c r="AJ87" s="32">
         <f t="shared" si="36"/>
-        <v>22.400000000000002</v>
-      </c>
-      <c r="AK87" s="6">
+        <v>0</v>
+      </c>
+      <c r="AK87" s="32">
         <f t="shared" si="37"/>
         <v>0</v>
       </c>
